--- a/products.xlsx
+++ b/products.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TIS\WebApp\my-table-project\distV6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TIS\WebApp\my-table-project\distV12Offline\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -267,7 +267,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="307">
   <si>
     <t>ردیف</t>
   </si>
@@ -742,6 +742,9 @@
   </si>
   <si>
     <t>Power supply 24V DC 1.5A</t>
+  </si>
+  <si>
+    <t>PIR-CEL/WALL-NC</t>
   </si>
   <si>
     <t xml:space="preserve">سنسور کنترل حضور اشخاص ،سقفی یا دیواری هوشمند شده با اتصال به پورت دیجیتال کلید یا پورت دیجیتال ماژول 10F یا پورت دیجیتال مبدل 4 کانال  </t>
@@ -993,9 +996,6 @@
     <t>آمپلی فایر تمام اهمی دارای صفحه نمایشگر، دارای 8 کلید ولوم جهت کنترل هر یک از خروجی ها، ورودی USB، بلوتوث، رادیو FM، دو درگاه ورودی AUX، خروجی AUX، سه ورودی میکروفن با کلید های کنترلی میکروفن ها، ریموت کنترل IR، ورودی برق 220 ولت </t>
   </si>
   <si>
-    <t>Amplyfire JX600-8</t>
-  </si>
-  <si>
     <t>8zone Audio Player , , share different source output X50 Watt each 4-8 ohms amplifier Streaming Audiot,  , Bluetooth , USB Mp3 Player, Aux In, Aux out.</t>
   </si>
   <si>
@@ -1050,9 +1050,6 @@
     <t>TIS-SPK-XC6-FLO</t>
   </si>
   <si>
-    <t>اسپیکر ئکوراتیو</t>
-  </si>
-  <si>
     <t>SPK-XC6-WALL</t>
   </si>
   <si>
@@ -1194,7 +1191,16 @@
     <t>TIS-DALI-DM-4C8A</t>
   </si>
   <si>
-    <t>PIR-CEL-WALL-NC</t>
+    <t>Amplifier JX600-8</t>
+  </si>
+  <si>
+    <t>Music Player WC</t>
+  </si>
+  <si>
+    <t>اسپیکر فریم لس 15</t>
+  </si>
+  <si>
+    <t>اسپیکر دکوراتیو</t>
   </si>
 </sst>
 </file>
@@ -2595,7 +2601,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="36576" bIns="32004" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -2664,7 +2670,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="18288" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="36576" bIns="32004" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -3065,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>54</v>
@@ -3101,16 +3107,16 @@
         <v>64</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="2">
@@ -3468,7 +3474,7 @@
         <v>18</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>130</v>
@@ -3549,7 +3555,7 @@
         <v>91</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>88</v>
@@ -3608,13 +3614,13 @@
         <v>90</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>304</v>
+        <v>155</v>
       </c>
       <c r="F20" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="2">
@@ -3633,16 +3639,16 @@
         <v>91</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="2">
@@ -3661,16 +3667,16 @@
         <v>91</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="2">
@@ -3689,16 +3695,16 @@
         <v>91</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="2">
@@ -3717,7 +3723,7 @@
         <v>91</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>111</v>
@@ -3807,7 +3813,7 @@
         <v>24</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>96</v>
@@ -3919,7 +3925,7 @@
         <v>23</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>95</v>
@@ -3941,7 +3947,7 @@
         <v>59</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>44</v>
@@ -3969,7 +3975,7 @@
         <v>59</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>45</v>
@@ -3997,7 +4003,7 @@
         <v>59</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>46</v>
@@ -4025,7 +4031,7 @@
         <v>59</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>47</v>
@@ -4053,7 +4059,7 @@
         <v>59</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>43</v>
@@ -4109,7 +4115,7 @@
         <v>59</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>48</v>
@@ -4137,7 +4143,7 @@
         <v>59</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>49</v>
@@ -4165,7 +4171,7 @@
         <v>59</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>50</v>
@@ -4193,7 +4199,7 @@
         <v>59</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>51</v>
@@ -4221,16 +4227,16 @@
         <v>59</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="2">
@@ -4249,16 +4255,16 @@
         <v>59</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="2">
@@ -4277,13 +4283,13 @@
         <v>63</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E44" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F44" s="24" t="s">
         <v>192</v>
-      </c>
-      <c r="F44" s="24" t="s">
-        <v>191</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>99</v>
@@ -4305,16 +4311,16 @@
         <v>63</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="2">
@@ -4414,19 +4420,19 @@
         <v>48</v>
       </c>
       <c r="C49" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="E49" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="E49" s="27" t="s">
-        <v>202</v>
-      </c>
       <c r="F49" s="25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H49" s="6"/>
       <c r="I49" s="2">
@@ -4442,19 +4448,19 @@
         <v>49</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F50" s="24" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H50" s="6"/>
       <c r="I50" s="2">
@@ -4470,19 +4476,19 @@
         <v>50</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D51" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F51" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="E51" s="27" t="s">
-        <v>211</v>
-      </c>
-      <c r="F51" s="25" t="s">
-        <v>212</v>
-      </c>
       <c r="G51" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H51" s="6"/>
       <c r="I51" s="2">
@@ -4498,19 +4504,19 @@
         <v>51</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H52" s="6"/>
       <c r="I52" s="2">
@@ -4526,17 +4532,19 @@
         <v>52</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="E53" s="8"/>
+        <v>221</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>304</v>
+      </c>
       <c r="F53" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H53" s="6"/>
       <c r="I53" s="2">
@@ -4552,19 +4560,19 @@
         <v>53</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H54" s="6"/>
       <c r="I54" s="2">
@@ -4580,19 +4588,19 @@
         <v>54</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D55" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="E55" s="8" t="s">
-        <v>227</v>
-      </c>
       <c r="F55" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H55" s="6"/>
       <c r="I55" s="2">
@@ -4608,19 +4616,19 @@
         <v>55</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H56" s="6"/>
       <c r="I56" s="2">
@@ -4636,19 +4644,19 @@
         <v>56</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>237</v>
+        <v>303</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>238</v>
       </c>
       <c r="G57" s="28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H57" s="6"/>
       <c r="I57" s="2">
@@ -4664,7 +4672,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>239</v>
@@ -4692,7 +4700,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>241</v>
@@ -4720,7 +4728,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>247</v>
@@ -4748,16 +4756,16 @@
         <v>60</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>250</v>
+        <v>305</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>252</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>254</v>
@@ -4776,7 +4784,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>250</v>
@@ -4785,10 +4793,10 @@
         <v>251</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G62" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H62" s="6"/>
       <c r="I62" s="2">
@@ -4804,7 +4812,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>250</v>
@@ -4813,10 +4821,10 @@
         <v>255</v>
       </c>
       <c r="F63" s="30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H63" s="6"/>
       <c r="I63" s="2">
@@ -4832,19 +4840,19 @@
         <v>63</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D64" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>257</v>
-      </c>
       <c r="F64" s="25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H64" s="6"/>
       <c r="I64" s="2">
@@ -4860,19 +4868,19 @@
         <v>64</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E65" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="F65" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="F65" s="25" t="s">
+      <c r="G65" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="H65" s="6"/>
       <c r="I65" s="2">
@@ -4888,19 +4896,19 @@
         <v>65</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D66" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="E66" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="F66" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="F66" s="25" t="s">
+      <c r="G66" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="H66" s="6"/>
       <c r="I66" s="2">
@@ -4916,19 +4924,19 @@
         <v>66</v>
       </c>
       <c r="C67" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="D67" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="E67" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="F67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="F67" s="9" t="s">
-        <v>276</v>
-      </c>
       <c r="G67" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H67" s="6"/>
       <c r="I67" s="2">
@@ -4944,19 +4952,19 @@
         <v>67</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D68" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="F68" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="F68" s="9" t="s">
+      <c r="G68" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="H68" s="6"/>
       <c r="I68" s="2">
@@ -4972,19 +4980,19 @@
         <v>68</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G69" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H69" s="6"/>
       <c r="I69" s="2">
@@ -5000,19 +5008,19 @@
         <v>69</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D70" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="E70" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>294</v>
-      </c>
       <c r="F70" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="G70" s="37" t="s">
         <v>296</v>
-      </c>
-      <c r="G70" s="37" t="s">
-        <v>297</v>
       </c>
       <c r="H70" s="6"/>
       <c r="I70" s="2">
@@ -5028,19 +5036,19 @@
         <v>70</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D71" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="F71" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F71" s="9" t="s">
+      <c r="G71" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>286</v>
       </c>
       <c r="H71" s="6"/>
       <c r="I71" s="2">
@@ -5056,19 +5064,19 @@
         <v>71</v>
       </c>
       <c r="C72" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="D72" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="E72" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>289</v>
       </c>
       <c r="H72" s="6"/>
       <c r="I72" s="2">
@@ -5084,19 +5092,19 @@
         <v>72</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D73" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="E73" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="F73" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="F73" s="9" t="s">
+      <c r="G73" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="H73" s="6"/>
       <c r="I73" s="2">
